--- a/OPENFC.xlsx
+++ b/OPENFC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51936089-48FF-447B-8EDC-FCEC1899C045}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016C4436-2753-4398-BDC7-314A8BC45D59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3C536319-8C24-4021-B9D4-FBD21F6BCA84}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="\a">[1]ยอดขาย!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN FC'!$A$2:$Q$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN FC'!$A$2:$Q$298</definedName>
     <definedName name="d">#REF!</definedName>
     <definedName name="Datalist">OFFSET('[2]Data-CPAC'!$A$1,0,0,COUNTA('[2]Data-CPAC'!$A:$A),COUNTA('[2]Data-CPAC'!$1:$1))</definedName>
     <definedName name="dfg">#REF!</definedName>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3860" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3873" uniqueCount="1121">
   <si>
     <t>เปิดโรงงาน</t>
   </si>
@@ -3453,6 +3453,12 @@
   </si>
   <si>
     <t>เปลี่ยนชื่อจาก สระกระโจม</t>
+  </si>
+  <si>
+    <t>FC414</t>
+  </si>
+  <si>
+    <t>ทับปุด 2</t>
   </si>
 </sst>
 </file>
@@ -3980,7 +3986,61 @@
     <cellStyle name="Normal 3" xfId="5" xr:uid="{B66B5600-A50E-4622-AF93-9F956B928450}"/>
     <cellStyle name="Normal_FC Type S -Update มิ.ย.54 2" xfId="1" xr:uid="{BD1075EE-4223-4491-8ED9-9574F7136865}"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -12143,7 +12203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E2B2200-77E3-4247-A157-690BD36C0F87}">
-  <dimension ref="A1:Q297"/>
+  <dimension ref="A1:Q298"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
@@ -25985,10 +26045,10 @@
         <v>414</v>
       </c>
       <c r="F272" s="28" t="s">
-        <v>419</v>
+        <v>1119</v>
       </c>
       <c r="G272" s="26" t="s">
-        <v>418</v>
+        <v>1120</v>
       </c>
       <c r="H272" s="28" t="s">
         <v>418</v>
@@ -26003,10 +26063,10 @@
         <v>11</v>
       </c>
       <c r="L272" s="30" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="M272" s="31">
-        <v>2554</v>
+        <v>2569</v>
       </c>
       <c r="N272" s="29"/>
       <c r="O272" s="31"/>
@@ -26016,10 +26076,10 @@
       </c>
     </row>
     <row r="273" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A273" s="43" t="s">
+      <c r="A273" s="29" t="s">
         <v>1051</v>
       </c>
-      <c r="B273" s="85" t="s">
+      <c r="B273" s="28" t="s">
         <v>1077</v>
       </c>
       <c r="C273" s="26" t="s">
@@ -26031,202 +26091,202 @@
       <c r="E273" s="26" t="s">
         <v>414</v>
       </c>
-      <c r="F273" s="33" t="s">
+      <c r="F273" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="G273" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="H273" s="28" t="s">
+        <v>418</v>
+      </c>
+      <c r="I273" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J273" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K273" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="L273" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="M273" s="31">
+        <v>2554</v>
+      </c>
+      <c r="N273" s="29"/>
+      <c r="O273" s="31"/>
+      <c r="P273" s="32"/>
+      <c r="Q273" s="28" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="274" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A274" s="43" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B274" s="85" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C274" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="D274" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="E274" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="F274" s="33" t="s">
         <v>420</v>
       </c>
-      <c r="G273" s="33" t="s">
+      <c r="G274" s="33" t="s">
         <v>421</v>
       </c>
-      <c r="H273" s="33" t="s">
+      <c r="H274" s="33" t="s">
         <v>418</v>
       </c>
-      <c r="I273" s="43" t="s">
+      <c r="I274" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="J273" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="K273" s="43" t="s">
+      <c r="J274" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="K274" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="L273" s="44" t="s">
+      <c r="L274" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="M273" s="31">
+      <c r="M274" s="31">
         <v>2557</v>
       </c>
-      <c r="N273" s="43"/>
-      <c r="O273" s="45"/>
-      <c r="P273" s="32"/>
-      <c r="Q273" s="33" t="s">
+      <c r="N274" s="43"/>
+      <c r="O274" s="45"/>
+      <c r="P274" s="32"/>
+      <c r="Q274" s="33" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="274" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A274" s="40" t="s">
+    <row r="275" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A275" s="40" t="s">
         <v>1051</v>
       </c>
-      <c r="B274" s="34" t="s">
+      <c r="B275" s="34" t="s">
         <v>422</v>
       </c>
-      <c r="C274" s="38" t="s">
+      <c r="C275" s="38" t="s">
         <v>422</v>
       </c>
-      <c r="D274" s="39" t="s">
+      <c r="D275" s="39" t="s">
         <v>423</v>
       </c>
-      <c r="E274" s="38" t="s">
+      <c r="E275" s="38" t="s">
         <v>422</v>
       </c>
-      <c r="F274" s="34" t="s">
+      <c r="F275" s="34" t="s">
         <v>424</v>
       </c>
-      <c r="G274" s="38" t="s">
+      <c r="G275" s="38" t="s">
         <v>425</v>
       </c>
-      <c r="H274" s="34" t="s">
+      <c r="H275" s="34" t="s">
         <v>411</v>
       </c>
-      <c r="I274" s="40" t="s">
+      <c r="I275" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J274" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="K274" s="40" t="s">
+      <c r="J275" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="K275" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="L274" s="41" t="s">
+      <c r="L275" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="M274" s="42">
+      <c r="M275" s="42">
         <v>2551</v>
       </c>
-      <c r="N274" s="40"/>
-      <c r="O274" s="42"/>
-      <c r="P274" s="21"/>
-      <c r="Q274" s="34" t="s">
+      <c r="N275" s="40"/>
+      <c r="O275" s="42"/>
+      <c r="P275" s="21"/>
+      <c r="Q275" s="34" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="275" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A275" s="10" t="s">
+    <row r="276" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A276" s="10" t="s">
         <v>1051</v>
       </c>
-      <c r="B275" s="9" t="s">
+      <c r="B276" s="9" t="s">
         <v>1078</v>
       </c>
-      <c r="C275" s="7" t="s">
+      <c r="C276" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="D275" s="8" t="s">
+      <c r="D276" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="E275" s="7" t="s">
+      <c r="E276" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="F275" s="9" t="s">
+      <c r="F276" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="G275" s="7" t="s">
+      <c r="G276" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="H275" s="9" t="s">
+      <c r="H276" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="I275" s="10" t="s">
+      <c r="I276" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J275" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="K275" s="10" t="s">
+      <c r="J276" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K276" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L275" s="11" t="s">
+      <c r="L276" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="M275" s="12">
+      <c r="M276" s="12">
         <v>2549</v>
       </c>
-      <c r="N275" s="10"/>
-      <c r="O275" s="12"/>
-      <c r="P275" s="13"/>
-      <c r="Q275" s="9" t="s">
+      <c r="N276" s="10"/>
+      <c r="O276" s="12"/>
+      <c r="P276" s="13"/>
+      <c r="Q276" s="9" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="276" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A276" s="43" t="s">
+    <row r="277" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A277" s="43" t="s">
         <v>1051</v>
       </c>
-      <c r="B276" s="33" t="s">
+      <c r="B277" s="33" t="s">
         <v>1082</v>
       </c>
-      <c r="C276" s="33" t="s">
+      <c r="C277" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="D276" s="33" t="s">
+      <c r="D277" s="33" t="s">
         <v>431</v>
       </c>
-      <c r="E276" s="33" t="s">
+      <c r="E277" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="F276" s="33" t="s">
+      <c r="F277" s="33" t="s">
         <v>432</v>
       </c>
-      <c r="G276" s="33" t="s">
+      <c r="G277" s="33" t="s">
         <v>433</v>
       </c>
-      <c r="H276" s="28" t="s">
+      <c r="H277" s="28" t="s">
         <v>385</v>
-      </c>
-      <c r="I276" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="J276" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="K276" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="L276" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="M276" s="31">
-        <v>2566</v>
-      </c>
-      <c r="N276" s="29"/>
-      <c r="O276" s="31"/>
-      <c r="P276" s="32"/>
-      <c r="Q276" s="28" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="277" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A277" s="29" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B277" s="82" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C277" s="26" t="s">
-        <v>430</v>
-      </c>
-      <c r="D277" s="26" t="s">
-        <v>431</v>
-      </c>
-      <c r="E277" s="26" t="s">
-        <v>430</v>
-      </c>
-      <c r="F277" s="28" t="s">
-        <v>1038</v>
-      </c>
-      <c r="G277" s="26" t="s">
-        <v>434</v>
-      </c>
-      <c r="H277" s="28" t="s">
-        <v>418</v>
       </c>
       <c r="I277" s="29" t="s">
         <v>23</v>
@@ -26238,109 +26298,109 @@
         <v>11</v>
       </c>
       <c r="L277" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="M277" s="29">
-        <v>2568</v>
+        <v>80</v>
+      </c>
+      <c r="M277" s="31">
+        <v>2566</v>
       </c>
       <c r="N277" s="29"/>
-      <c r="O277" s="29"/>
+      <c r="O277" s="31"/>
       <c r="P277" s="32"/>
       <c r="Q277" s="28" t="s">
         <v>1045</v>
       </c>
     </row>
     <row r="278" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A278" s="40" t="s">
+      <c r="A278" s="29" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B278" s="82" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C278" s="26" t="s">
+        <v>430</v>
+      </c>
+      <c r="D278" s="26" t="s">
+        <v>431</v>
+      </c>
+      <c r="E278" s="26" t="s">
+        <v>430</v>
+      </c>
+      <c r="F278" s="28" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G278" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="H278" s="28" t="s">
+        <v>418</v>
+      </c>
+      <c r="I278" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J278" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K278" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="L278" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M278" s="29">
+        <v>2568</v>
+      </c>
+      <c r="N278" s="29"/>
+      <c r="O278" s="29"/>
+      <c r="P278" s="32"/>
+      <c r="Q278" s="28" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="279" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A279" s="40" t="s">
         <v>1048</v>
       </c>
-      <c r="B278" s="84" t="s">
+      <c r="B279" s="84" t="s">
         <v>1059</v>
       </c>
-      <c r="C278" s="38" t="s">
+      <c r="C279" s="38" t="s">
         <v>453</v>
       </c>
-      <c r="D278" s="39" t="s">
+      <c r="D279" s="39" t="s">
         <v>454</v>
       </c>
-      <c r="E278" s="38" t="s">
+      <c r="E279" s="38" t="s">
         <v>453</v>
       </c>
-      <c r="F278" s="34" t="s">
+      <c r="F279" s="34" t="s">
         <v>455</v>
       </c>
-      <c r="G278" s="38" t="s">
+      <c r="G279" s="38" t="s">
         <v>456</v>
       </c>
-      <c r="H278" s="34" t="s">
+      <c r="H279" s="34" t="s">
         <v>457</v>
       </c>
-      <c r="I278" s="40" t="s">
+      <c r="I279" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J278" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="K278" s="40" t="s">
+      <c r="J279" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="K279" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="L278" s="41" t="s">
+      <c r="L279" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="M278" s="42">
+      <c r="M279" s="42">
         <v>2549</v>
       </c>
-      <c r="N278" s="40"/>
-      <c r="O278" s="42"/>
-      <c r="P278" s="21"/>
-      <c r="Q278" s="34" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="279" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A279" s="29" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B279" s="82" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C279" s="26" t="s">
-        <v>458</v>
-      </c>
-      <c r="D279" s="27" t="s">
-        <v>459</v>
-      </c>
-      <c r="E279" s="26" t="s">
-        <v>458</v>
-      </c>
-      <c r="F279" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="G279" s="26" t="s">
-        <v>462</v>
-      </c>
-      <c r="H279" s="28" t="s">
-        <v>460</v>
-      </c>
-      <c r="I279" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="J279" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="K279" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="L279" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="M279" s="31">
-        <v>2547</v>
-      </c>
-      <c r="N279" s="29"/>
-      <c r="O279" s="31"/>
-      <c r="P279" s="32"/>
-      <c r="Q279" s="28" t="s">
+      <c r="N279" s="40"/>
+      <c r="O279" s="42"/>
+      <c r="P279" s="21"/>
+      <c r="Q279" s="34" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -26360,14 +26420,14 @@
       <c r="E280" s="26" t="s">
         <v>458</v>
       </c>
-      <c r="F280" s="33" t="s">
-        <v>463</v>
-      </c>
-      <c r="G280" s="33" t="s">
-        <v>464</v>
+      <c r="F280" s="28" t="s">
+        <v>461</v>
+      </c>
+      <c r="G280" s="26" t="s">
+        <v>462</v>
       </c>
       <c r="H280" s="28" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="I280" s="29" t="s">
         <v>23</v>
@@ -26382,7 +26442,7 @@
         <v>41</v>
       </c>
       <c r="M280" s="31">
-        <v>2557</v>
+        <v>2547</v>
       </c>
       <c r="N280" s="29"/>
       <c r="O280" s="31"/>
@@ -26407,14 +26467,14 @@
       <c r="E281" s="26" t="s">
         <v>458</v>
       </c>
-      <c r="F281" s="28" t="s">
-        <v>466</v>
-      </c>
-      <c r="G281" s="26" t="s">
-        <v>467</v>
+      <c r="F281" s="33" t="s">
+        <v>463</v>
+      </c>
+      <c r="G281" s="33" t="s">
+        <v>464</v>
       </c>
       <c r="H281" s="28" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="I281" s="29" t="s">
         <v>23</v>
@@ -26426,10 +26486,10 @@
         <v>11</v>
       </c>
       <c r="L281" s="30" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="M281" s="31">
-        <v>2564</v>
+        <v>2557</v>
       </c>
       <c r="N281" s="29"/>
       <c r="O281" s="31"/>
@@ -26454,11 +26514,11 @@
       <c r="E282" s="26" t="s">
         <v>458</v>
       </c>
-      <c r="F282" s="33" t="s">
-        <v>468</v>
-      </c>
-      <c r="G282" s="56" t="s">
-        <v>469</v>
+      <c r="F282" s="28" t="s">
+        <v>466</v>
+      </c>
+      <c r="G282" s="26" t="s">
+        <v>467</v>
       </c>
       <c r="H282" s="28" t="s">
         <v>460</v>
@@ -26472,13 +26532,13 @@
       <c r="K282" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="L282" s="29" t="s">
-        <v>36</v>
+      <c r="L282" s="30" t="s">
+        <v>93</v>
       </c>
       <c r="M282" s="31">
-        <v>2567</v>
-      </c>
-      <c r="N282" s="53"/>
+        <v>2564</v>
+      </c>
+      <c r="N282" s="29"/>
       <c r="O282" s="31"/>
       <c r="P282" s="32"/>
       <c r="Q282" s="28" t="s">
@@ -26486,143 +26546,143 @@
       </c>
     </row>
     <row r="283" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A283" s="40" t="s">
+      <c r="A283" s="29" t="s">
         <v>1048</v>
       </c>
-      <c r="B283" s="99" t="s">
+      <c r="B283" s="82" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C283" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="D283" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="E283" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="F283" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="G283" s="56" t="s">
+        <v>469</v>
+      </c>
+      <c r="H283" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="I283" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J283" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K283" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="L283" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="M283" s="31">
+        <v>2567</v>
+      </c>
+      <c r="N283" s="53"/>
+      <c r="O283" s="31"/>
+      <c r="P283" s="32"/>
+      <c r="Q283" s="28" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="284" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A284" s="40" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B284" s="99" t="s">
         <v>470</v>
       </c>
-      <c r="C283" s="38" t="s">
+      <c r="C284" s="38" t="s">
         <v>470</v>
       </c>
-      <c r="D283" s="39" t="s">
+      <c r="D284" s="39" t="s">
         <v>471</v>
       </c>
-      <c r="E283" s="38" t="s">
+      <c r="E284" s="38" t="s">
         <v>470</v>
       </c>
-      <c r="F283" s="34" t="s">
+      <c r="F284" s="34" t="s">
         <v>472</v>
       </c>
-      <c r="G283" s="38" t="s">
+      <c r="G284" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="H283" s="34" t="s">
+      <c r="H284" s="34" t="s">
         <v>474</v>
       </c>
-      <c r="I283" s="40" t="s">
+      <c r="I284" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J283" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="K283" s="40" t="s">
+      <c r="J284" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="K284" s="40" t="s">
         <v>1036</v>
       </c>
-      <c r="L283" s="41" t="s">
+      <c r="L284" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="M283" s="42">
+      <c r="M284" s="42">
         <v>2550</v>
       </c>
-      <c r="N283" s="40"/>
-      <c r="O283" s="42"/>
-      <c r="P283" s="21"/>
-      <c r="Q283" s="34" t="s">
+      <c r="N284" s="40"/>
+      <c r="O284" s="42"/>
+      <c r="P284" s="21"/>
+      <c r="Q284" s="34" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="284" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A284" s="49" t="s">
+    <row r="285" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A285" s="49" t="s">
         <v>1048</v>
       </c>
-      <c r="B284" s="86" t="s">
+      <c r="B285" s="86" t="s">
         <v>475</v>
       </c>
-      <c r="C284" s="8" t="s">
+      <c r="C285" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="D284" s="15" t="s">
+      <c r="D285" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="E284" s="8" t="s">
+      <c r="E285" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="F284" s="15" t="s">
+      <c r="F285" s="15" t="s">
         <v>478</v>
       </c>
-      <c r="G284" s="8" t="s">
+      <c r="G285" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="H284" s="15" t="s">
+      <c r="H285" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="I284" s="49" t="s">
+      <c r="I285" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="J284" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="K284" s="49" t="s">
+      <c r="J285" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="K285" s="49" t="s">
         <v>1036</v>
       </c>
-      <c r="L284" s="50" t="s">
+      <c r="L285" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="M284" s="12">
+      <c r="M285" s="12">
         <v>2557</v>
       </c>
-      <c r="N284" s="49"/>
-      <c r="O284" s="51"/>
-      <c r="P284" s="13"/>
-      <c r="Q284" s="15" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="285" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A285" s="29" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B285" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="C285" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="D285" s="27" t="s">
-        <v>486</v>
-      </c>
-      <c r="E285" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="F285" s="28" t="s">
-        <v>487</v>
-      </c>
-      <c r="G285" s="26" t="s">
-        <v>488</v>
-      </c>
-      <c r="H285" s="28" t="s">
-        <v>485</v>
-      </c>
-      <c r="I285" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="J285" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="K285" s="29" t="s">
-        <v>1037</v>
-      </c>
-      <c r="L285" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="M285" s="31">
-        <v>2553</v>
-      </c>
-      <c r="N285" s="29"/>
-      <c r="O285" s="31"/>
-      <c r="P285" s="32"/>
-      <c r="Q285" s="28" t="s">
+      <c r="N285" s="49"/>
+      <c r="O285" s="51"/>
+      <c r="P285" s="13"/>
+      <c r="Q285" s="15" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -26643,10 +26703,10 @@
         <v>480</v>
       </c>
       <c r="F286" s="28" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="G286" s="26" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="H286" s="28" t="s">
         <v>485</v>
@@ -26661,10 +26721,10 @@
         <v>1037</v>
       </c>
       <c r="L286" s="30" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="M286" s="31">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="N286" s="29"/>
       <c r="O286" s="31"/>
@@ -26674,51 +26734,49 @@
       </c>
     </row>
     <row r="287" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A287" s="10" t="s">
+      <c r="A287" s="29" t="s">
         <v>1048</v>
       </c>
-      <c r="B287" s="9" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C287" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="D287" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="E287" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="F287" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="G287" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="H287" s="9" t="s">
+      <c r="B287" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="C287" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="D287" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="E287" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="F287" s="28" t="s">
+        <v>492</v>
+      </c>
+      <c r="G287" s="26" t="s">
+        <v>493</v>
+      </c>
+      <c r="H287" s="28" t="s">
         <v>485</v>
       </c>
-      <c r="I287" s="10" t="s">
+      <c r="I287" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J287" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="K287" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="L287" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M287" s="12">
-        <v>2548</v>
-      </c>
-      <c r="N287" s="10"/>
-      <c r="O287" s="12"/>
-      <c r="P287" s="13" t="s">
-        <v>1109</v>
-      </c>
-      <c r="Q287" s="9" t="s">
+      <c r="J287" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K287" s="29" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L287" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="M287" s="31">
+        <v>2555</v>
+      </c>
+      <c r="N287" s="29"/>
+      <c r="O287" s="31"/>
+      <c r="P287" s="32"/>
+      <c r="Q287" s="28" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -26738,11 +26796,11 @@
       <c r="E288" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="F288" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="G288" s="15" t="s">
-        <v>503</v>
+      <c r="F288" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="G288" s="7" t="s">
+        <v>501</v>
       </c>
       <c r="H288" s="9" t="s">
         <v>485</v>
@@ -26757,14 +26815,16 @@
         <v>11</v>
       </c>
       <c r="L288" s="11" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="M288" s="12">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="N288" s="10"/>
       <c r="O288" s="12"/>
-      <c r="P288" s="13"/>
+      <c r="P288" s="13" t="s">
+        <v>1109</v>
+      </c>
       <c r="Q288" s="9" t="s">
         <v>1045</v>
       </c>
@@ -26785,11 +26845,11 @@
       <c r="E289" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="F289" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="G289" s="7" t="s">
-        <v>505</v>
+      <c r="F289" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="G289" s="15" t="s">
+        <v>503</v>
       </c>
       <c r="H289" s="9" t="s">
         <v>485</v>
@@ -26807,7 +26867,7 @@
         <v>62</v>
       </c>
       <c r="M289" s="12">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="N289" s="10"/>
       <c r="O289" s="12"/>
@@ -26833,10 +26893,10 @@
         <v>496</v>
       </c>
       <c r="F290" s="9" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G290" s="7" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="H290" s="9" t="s">
         <v>485</v>
@@ -26845,72 +26905,70 @@
         <v>23</v>
       </c>
       <c r="J290" s="10" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K290" s="10" t="s">
         <v>11</v>
       </c>
       <c r="L290" s="11" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="M290" s="12">
-        <v>2546</v>
+        <v>2555</v>
       </c>
       <c r="N290" s="10"/>
       <c r="O290" s="12"/>
-      <c r="P290" s="13" t="s">
-        <v>1110</v>
-      </c>
+      <c r="P290" s="13"/>
       <c r="Q290" s="9" t="s">
         <v>1045</v>
       </c>
     </row>
     <row r="291" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A291" s="29" t="s">
+      <c r="A291" s="10" t="s">
         <v>1048</v>
       </c>
-      <c r="B291" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="C291" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="D291" s="33" t="s">
-        <v>489</v>
-      </c>
-      <c r="E291" s="33" t="s">
-        <v>494</v>
-      </c>
-      <c r="F291" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="G291" s="33" t="s">
-        <v>1115</v>
-      </c>
-      <c r="H291" s="33" t="s">
+      <c r="B291" s="9" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E291" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="F291" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="G291" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="H291" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="I291" s="43" t="s">
+      <c r="I291" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J291" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="K291" s="43" t="s">
+      <c r="J291" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K291" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L291" s="44" t="s">
+      <c r="L291" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="M291" s="31">
-        <v>2563</v>
-      </c>
-      <c r="N291" s="43"/>
-      <c r="O291" s="45"/>
-      <c r="P291" s="32" t="s">
-        <v>1116</v>
-      </c>
-      <c r="Q291" s="33" t="s">
+      <c r="M291" s="12">
+        <v>2546</v>
+      </c>
+      <c r="N291" s="10"/>
+      <c r="O291" s="12"/>
+      <c r="P291" s="13" t="s">
+        <v>1110</v>
+      </c>
+      <c r="Q291" s="9" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -26928,13 +26986,13 @@
         <v>489</v>
       </c>
       <c r="E292" s="33" t="s">
-        <v>490</v>
-      </c>
-      <c r="F292" s="28" t="s">
-        <v>491</v>
-      </c>
-      <c r="G292" s="26" t="s">
-        <v>1117</v>
+        <v>494</v>
+      </c>
+      <c r="F292" s="33" t="s">
+        <v>495</v>
+      </c>
+      <c r="G292" s="33" t="s">
+        <v>1115</v>
       </c>
       <c r="H292" s="33" t="s">
         <v>485</v>
@@ -26949,15 +27007,15 @@
         <v>11</v>
       </c>
       <c r="L292" s="44" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="M292" s="31">
-        <v>2554</v>
+        <v>2563</v>
       </c>
       <c r="N292" s="43"/>
       <c r="O292" s="45"/>
       <c r="P292" s="32" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="Q292" s="33" t="s">
         <v>1045</v>
@@ -26974,16 +27032,16 @@
         <v>480</v>
       </c>
       <c r="D293" s="33" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E293" s="33" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="F293" s="28" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="G293" s="26" t="s">
-        <v>484</v>
+        <v>1117</v>
       </c>
       <c r="H293" s="33" t="s">
         <v>485</v>
@@ -27001,229 +27059,300 @@
         <v>35</v>
       </c>
       <c r="M293" s="31">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="N293" s="43"/>
       <c r="O293" s="45"/>
-      <c r="P293" s="32"/>
+      <c r="P293" s="32" t="s">
+        <v>1118</v>
+      </c>
       <c r="Q293" s="33" t="s">
         <v>1045</v>
       </c>
     </row>
     <row r="294" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A294" s="46" t="s">
+      <c r="A294" s="29" t="s">
         <v>1048</v>
       </c>
-      <c r="B294" s="18" t="s">
+      <c r="B294" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="C294" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="D294" s="33" t="s">
+        <v>481</v>
+      </c>
+      <c r="E294" s="33" t="s">
+        <v>482</v>
+      </c>
+      <c r="F294" s="28" t="s">
+        <v>483</v>
+      </c>
+      <c r="G294" s="26" t="s">
+        <v>484</v>
+      </c>
+      <c r="H294" s="33" t="s">
+        <v>485</v>
+      </c>
+      <c r="I294" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="J294" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="K294" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="L294" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="M294" s="31">
+        <v>2552</v>
+      </c>
+      <c r="N294" s="43"/>
+      <c r="O294" s="45"/>
+      <c r="P294" s="32"/>
+      <c r="Q294" s="33" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="295" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A295" s="46" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B295" s="18" t="s">
         <v>506</v>
       </c>
-      <c r="C294" s="18" t="s">
+      <c r="C295" s="18" t="s">
         <v>506</v>
       </c>
-      <c r="D294" s="18" t="s">
+      <c r="D295" s="18" t="s">
         <v>507</v>
       </c>
-      <c r="E294" s="18" t="s">
+      <c r="E295" s="18" t="s">
         <v>506</v>
       </c>
-      <c r="F294" s="18" t="s">
+      <c r="F295" s="18" t="s">
         <v>508</v>
       </c>
-      <c r="G294" s="18" t="s">
+      <c r="G295" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="H294" s="18" t="s">
+      <c r="H295" s="18" t="s">
         <v>457</v>
       </c>
-      <c r="I294" s="46" t="s">
+      <c r="I295" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="J294" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="K294" s="46" t="s">
+      <c r="J295" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K295" s="46" t="s">
         <v>1036</v>
       </c>
-      <c r="L294" s="47" t="s">
+      <c r="L295" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="M294" s="42">
+      <c r="M295" s="42">
         <v>2556</v>
       </c>
-      <c r="N294" s="46"/>
-      <c r="O294" s="48"/>
-      <c r="P294" s="21"/>
-      <c r="Q294" s="18" t="s">
+      <c r="N295" s="46"/>
+      <c r="O295" s="48"/>
+      <c r="P295" s="21"/>
+      <c r="Q295" s="18" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="295" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A295" s="40" t="s">
+    <row r="296" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A296" s="40" t="s">
         <v>1048</v>
       </c>
-      <c r="B295" s="34" t="s">
+      <c r="B296" s="34" t="s">
         <v>1060</v>
       </c>
-      <c r="C295" s="38" t="s">
+      <c r="C296" s="38" t="s">
         <v>510</v>
       </c>
-      <c r="D295" s="39" t="s">
+      <c r="D296" s="39" t="s">
         <v>511</v>
       </c>
-      <c r="E295" s="38" t="s">
+      <c r="E296" s="38" t="s">
         <v>510</v>
       </c>
-      <c r="F295" s="34" t="s">
+      <c r="F296" s="34" t="s">
         <v>512</v>
       </c>
-      <c r="G295" s="38" t="s">
+      <c r="G296" s="38" t="s">
         <v>513</v>
       </c>
-      <c r="H295" s="34" t="s">
+      <c r="H296" s="34" t="s">
         <v>514</v>
       </c>
-      <c r="I295" s="40" t="s">
+      <c r="I296" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J295" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="K295" s="40" t="s">
+      <c r="J296" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="K296" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="L295" s="41" t="s">
+      <c r="L296" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="M295" s="42">
+      <c r="M296" s="42">
         <v>2549</v>
       </c>
-      <c r="N295" s="40"/>
-      <c r="O295" s="42"/>
-      <c r="P295" s="21"/>
-      <c r="Q295" s="34" t="s">
+      <c r="N296" s="40"/>
+      <c r="O296" s="42"/>
+      <c r="P296" s="21"/>
+      <c r="Q296" s="34" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="296" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A296" s="29" t="s">
+    <row r="297" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A297" s="29" t="s">
         <v>1048</v>
       </c>
-      <c r="B296" s="28" t="s">
+      <c r="B297" s="28" t="s">
         <v>520</v>
       </c>
-      <c r="C296" s="26" t="s">
+      <c r="C297" s="26" t="s">
         <v>520</v>
       </c>
-      <c r="D296" s="27" t="s">
+      <c r="D297" s="27" t="s">
         <v>521</v>
       </c>
-      <c r="E296" s="26" t="s">
+      <c r="E297" s="26" t="s">
         <v>520</v>
       </c>
-      <c r="F296" s="28" t="s">
+      <c r="F297" s="28" t="s">
         <v>522</v>
       </c>
-      <c r="G296" s="26" t="s">
+      <c r="G297" s="26" t="s">
         <v>457</v>
       </c>
-      <c r="H296" s="28" t="s">
+      <c r="H297" s="28" t="s">
         <v>457</v>
       </c>
-      <c r="I296" s="29" t="s">
+      <c r="I297" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J296" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="K296" s="29" t="s">
+      <c r="J297" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K297" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="L296" s="30" t="s">
+      <c r="L297" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="M296" s="31">
+      <c r="M297" s="31">
         <v>2543</v>
       </c>
-      <c r="N296" s="29"/>
-      <c r="O296" s="31"/>
-      <c r="P296" s="32"/>
-      <c r="Q296" s="28" t="s">
+      <c r="N297" s="29"/>
+      <c r="O297" s="31"/>
+      <c r="P297" s="32"/>
+      <c r="Q297" s="28" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="297" spans="1:17" ht="17.5" thickBot="1">
-      <c r="A297" s="10" t="s">
+    <row r="298" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A298" s="10" t="s">
         <v>1048</v>
       </c>
-      <c r="B297" s="9" t="s">
+      <c r="B298" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="C297" s="7" t="s">
+      <c r="C298" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="D297" s="8" t="s">
+      <c r="D298" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="E297" s="7" t="s">
+      <c r="E298" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="F297" s="9" t="s">
+      <c r="F298" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="G297" s="7" t="s">
+      <c r="G298" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="H297" s="9" t="s">
+      <c r="H298" s="9" t="s">
         <v>457</v>
       </c>
-      <c r="I297" s="10" t="s">
+      <c r="I298" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J297" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="K297" s="10" t="s">
+      <c r="J298" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K298" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L297" s="11" t="s">
+      <c r="L298" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="M297" s="12">
+      <c r="M298" s="12">
         <v>2546</v>
       </c>
-      <c r="N297" s="10"/>
-      <c r="O297" s="12"/>
-      <c r="P297" s="13"/>
-      <c r="Q297" s="109" t="s">
+      <c r="N298" s="10"/>
+      <c r="O298" s="12"/>
+      <c r="P298" s="13"/>
+      <c r="Q298" s="109" t="s">
         <v>1045</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q297" xr:uid="{EEF4DB50-2D81-44EF-A62B-379133D03144}">
-    <sortState ref="A3:Q297">
-      <sortCondition ref="A3:A297"/>
-      <sortCondition ref="E3:E297"/>
+  <autoFilter ref="A2:Q298" xr:uid="{EEF4DB50-2D81-44EF-A62B-379133D03144}">
+    <sortState ref="A3:Q298">
+      <sortCondition ref="A3:A298"/>
+      <sortCondition ref="E3:E298"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A3:R297">
-    <sortCondition ref="J3:J297"/>
-    <sortCondition ref="O3:O297"/>
+  <sortState ref="A3:R298">
+    <sortCondition ref="J3:J298"/>
+    <sortCondition ref="O3:O298"/>
   </sortState>
   <mergeCells count="2">
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="M2 O2">
-    <cfRule type="cellIs" dxfId="38" priority="50" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="56" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2">
-    <cfRule type="cellIs" dxfId="37" priority="47" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="53" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K139 J296:K65340 K295 J93:K119 J141:K214 J121:K138 J1:K91 J216:K293">
+  <conditionalFormatting sqref="K139 J297:K65341 K296 J93:K119 J141:K214 J121:K138 J1:K91 J216:K270 J272:K294">
+    <cfRule type="cellIs" dxfId="42" priority="43" stopIfTrue="1" operator="equal">
+      <formula>"ปิดชั่วคราว"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="44" stopIfTrue="1" operator="equal">
+      <formula>"CLOSE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="45" stopIfTrue="1" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J270:K270 J272:K274">
+    <cfRule type="cellIs" dxfId="39" priority="40" stopIfTrue="1" operator="equal">
+      <formula>"ปิดชั่วคราว"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="41" stopIfTrue="1" operator="equal">
+      <formula>"CLOSE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="42" stopIfTrue="1" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J140:K140">
     <cfRule type="cellIs" dxfId="36" priority="37" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
@@ -27234,7 +27363,7 @@
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J270:K273">
+  <conditionalFormatting sqref="J139">
     <cfRule type="cellIs" dxfId="33" priority="34" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
@@ -27245,29 +27374,29 @@
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J140:K140">
-    <cfRule type="cellIs" dxfId="30" priority="31" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="J92">
+    <cfRule type="cellIs" dxfId="30" priority="29" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="32" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="30" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="33" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="31" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J139">
-    <cfRule type="cellIs" dxfId="27" priority="28" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="K120">
+    <cfRule type="cellIs" dxfId="27" priority="26" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="29" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="27" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="30" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="28" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J92">
+  <conditionalFormatting sqref="J120">
     <cfRule type="cellIs" dxfId="24" priority="23" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
@@ -27278,7 +27407,7 @@
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K120">
+  <conditionalFormatting sqref="J295">
     <cfRule type="cellIs" dxfId="21" priority="20" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
@@ -27289,7 +27418,7 @@
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J120">
+  <conditionalFormatting sqref="K295">
     <cfRule type="cellIs" dxfId="18" priority="17" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
@@ -27300,7 +27429,7 @@
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J294">
+  <conditionalFormatting sqref="J296">
     <cfRule type="cellIs" dxfId="15" priority="14" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
@@ -27311,7 +27440,7 @@
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K294">
+  <conditionalFormatting sqref="K92">
     <cfRule type="cellIs" dxfId="12" priority="11" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
@@ -27322,34 +27451,34 @@
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J295">
-    <cfRule type="cellIs" dxfId="9" priority="8" stopIfTrue="1" operator="equal">
-      <formula>"ปิดชั่วคราว"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" stopIfTrue="1" operator="equal">
-      <formula>"CLOSE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="10" stopIfTrue="1" operator="equal">
-      <formula>"OPEN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K92">
-    <cfRule type="cellIs" dxfId="6" priority="5" stopIfTrue="1" operator="equal">
-      <formula>"ปิดชั่วคราว"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" stopIfTrue="1" operator="equal">
-      <formula>"CLOSE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="7" stopIfTrue="1" operator="equal">
-      <formula>"OPEN"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N69:O69">
-    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J215:K215">
+    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="equal">
+      <formula>"ปิดชั่วคราว"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="equal">
+      <formula>"CLOSE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J271:K271">
+    <cfRule type="cellIs" dxfId="5" priority="4" stopIfTrue="1" operator="equal">
+      <formula>"ปิดชั่วคราว"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" stopIfTrue="1" operator="equal">
+      <formula>"CLOSE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" stopIfTrue="1" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J271:K271">
     <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>

--- a/OPENFC.xlsx
+++ b/OPENFC.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016C4436-2753-4398-BDC7-314A8BC45D59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16700699-CFED-4208-ACE3-E2F4F3624330}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3C536319-8C24-4021-B9D4-FBD21F6BCA84}"/>
   </bookViews>
   <sheets>
     <sheet name="OPEN FC" sheetId="1" r:id="rId1"/>
+    <sheet name="PLAN" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="\a">[1]ยอดขาย!#REF!</definedName>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3873" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="1232">
   <si>
     <t>เปิดโรงงาน</t>
   </si>
@@ -3459,6 +3460,339 @@
   </si>
   <si>
     <t>ทับปุด 2</t>
+  </si>
+  <si>
+    <t>PC031</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>บจก.พี.คอนกรีตโปรดักส์</t>
+  </si>
+  <si>
+    <t>FR085</t>
+  </si>
+  <si>
+    <t>PC002</t>
+  </si>
+  <si>
+    <t>สันกำแพง</t>
+  </si>
+  <si>
+    <t>PC001</t>
+  </si>
+  <si>
+    <t>บจก.วี.คอนโปรดักส์</t>
+  </si>
+  <si>
+    <t>FR132</t>
+  </si>
+  <si>
+    <t>PC033</t>
+  </si>
+  <si>
+    <t>หจก.เผ่าพงษ์ศาล</t>
+  </si>
+  <si>
+    <t>FR205</t>
+  </si>
+  <si>
+    <t>PC051</t>
+  </si>
+  <si>
+    <t>แม่สอด</t>
+  </si>
+  <si>
+    <t>PC029</t>
+  </si>
+  <si>
+    <t>ฝาง</t>
+  </si>
+  <si>
+    <t>PC053</t>
+  </si>
+  <si>
+    <t>FR096</t>
+  </si>
+  <si>
+    <t>บจก.สมุยคอนกรีต</t>
+  </si>
+  <si>
+    <t>PC014</t>
+  </si>
+  <si>
+    <t>เกาะสมุย</t>
+  </si>
+  <si>
+    <t>บจก.นันทวัฒน์การโยธา</t>
+  </si>
+  <si>
+    <t>FR321</t>
+  </si>
+  <si>
+    <t>PC060</t>
+  </si>
+  <si>
+    <t>บางกล่ำ</t>
+  </si>
+  <si>
+    <t>PC056</t>
+  </si>
+  <si>
+    <t>PC019</t>
+  </si>
+  <si>
+    <t>PC035</t>
+  </si>
+  <si>
+    <t>PC012</t>
+  </si>
+  <si>
+    <t>บางม่วง</t>
+  </si>
+  <si>
+    <t>PC028</t>
+  </si>
+  <si>
+    <t>บจก.ระวีกิจ</t>
+  </si>
+  <si>
+    <t>FR127</t>
+  </si>
+  <si>
+    <t>PC030</t>
+  </si>
+  <si>
+    <t>สามพราน</t>
+  </si>
+  <si>
+    <t>หจก.เพชรบุรีเจริญ แผ่นพื้นคอนกรีต</t>
+  </si>
+  <si>
+    <t>FR199</t>
+  </si>
+  <si>
+    <t>PC048</t>
+  </si>
+  <si>
+    <t>บจก.สต็อคโฮม 88</t>
+  </si>
+  <si>
+    <t>FR207</t>
+  </si>
+  <si>
+    <t>PC052</t>
+  </si>
+  <si>
+    <t>อรัญประเทศ</t>
+  </si>
+  <si>
+    <t>PC039</t>
+  </si>
+  <si>
+    <t>หนองใหญ่</t>
+  </si>
+  <si>
+    <t>PC059</t>
+  </si>
+  <si>
+    <t>ท่าเรือ</t>
+  </si>
+  <si>
+    <t>FR210</t>
+  </si>
+  <si>
+    <t>หจก.ที เค ซี โปรดักส์</t>
+  </si>
+  <si>
+    <t>PC054</t>
+  </si>
+  <si>
+    <t>หจก.พลับพลาคอนกรีต</t>
+  </si>
+  <si>
+    <t>FR164</t>
+  </si>
+  <si>
+    <t>PC042</t>
+  </si>
+  <si>
+    <t>PC041</t>
+  </si>
+  <si>
+    <t>PC049</t>
+  </si>
+  <si>
+    <t>PC044</t>
+  </si>
+  <si>
+    <t>หจก.เคหะภัณฑ์ คอนกรีต(2008)</t>
+  </si>
+  <si>
+    <t>FR166</t>
+  </si>
+  <si>
+    <t>PC037</t>
+  </si>
+  <si>
+    <t>นางรอง</t>
+  </si>
+  <si>
+    <t>หจก.เทพประทานพรวัสดุภัณฑ์</t>
+  </si>
+  <si>
+    <t>FR104</t>
+  </si>
+  <si>
+    <t>PC018</t>
+  </si>
+  <si>
+    <t>หจก.ที.อาร์.คอนกรีต</t>
+  </si>
+  <si>
+    <t>FR044</t>
+  </si>
+  <si>
+    <t>PC015</t>
+  </si>
+  <si>
+    <t>PC034</t>
+  </si>
+  <si>
+    <t>คอนสวรรค์</t>
+  </si>
+  <si>
+    <t>หจก.บุญพารวย</t>
+  </si>
+  <si>
+    <t>FR106</t>
+  </si>
+  <si>
+    <t>PC021</t>
+  </si>
+  <si>
+    <t>ปักธงชัย</t>
+  </si>
+  <si>
+    <t>PC055</t>
+  </si>
+  <si>
+    <t>ตาก</t>
+  </si>
+  <si>
+    <t>นครปฐม</t>
+  </si>
+  <si>
+    <t>Precast</t>
+  </si>
+  <si>
+    <t>บจก.พรีคอน (ประเทศไทย)</t>
+  </si>
+  <si>
+    <t>FR346</t>
+  </si>
+  <si>
+    <t>บจก.อลังการคอนกรีต</t>
+  </si>
+  <si>
+    <t>อลังการคอนกรีต</t>
+  </si>
+  <si>
+    <t>พรีคอน</t>
+  </si>
+  <si>
+    <t>FR345</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>บริษัท</t>
+  </si>
+  <si>
+    <t>วันที่คาดว่าจะเปิดผลิต</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>การดำเนินการ</t>
+  </si>
+  <si>
+    <t>เหนือ</t>
+  </si>
+  <si>
+    <t>หล่มเก่า</t>
+  </si>
+  <si>
+    <t>ON PROCESS</t>
+  </si>
+  <si>
+    <t>ติดเรื่องการนำโฉนดของเจ้าของเดิมออกจากธนาคาร เพื่อไปดำเนินการต่อ (ประมาณกลาง สค.)</t>
+  </si>
+  <si>
+    <t>ใต้</t>
+  </si>
+  <si>
+    <t>กระโสม</t>
+  </si>
+  <si>
+    <t>เครื่องจักรติดตั้ง ประมาณเดือน 8/2569 , ปัญหาเรื่องคนงานชุดเก่าทิ้งงาน</t>
+  </si>
+  <si>
+    <t>ตะวันออก</t>
+  </si>
+  <si>
+    <t>VS คอนกรีต 2</t>
+  </si>
+  <si>
+    <t>NX</t>
+  </si>
+  <si>
+    <t>บูรพา ท่าใหม่</t>
+  </si>
+  <si>
+    <t>บจก.บูรพาคอนกรีตแอนคอนสตั๊กชั่น</t>
+  </si>
+  <si>
+    <t xml:space="preserve">รอการปรับปรุงระบบsafety และสิ่งแวดล้อม F27,F28  </t>
+  </si>
+  <si>
+    <t>บ้านสร้าง</t>
+  </si>
+  <si>
+    <t>CANCEL</t>
+  </si>
+  <si>
+    <t>รอดูสถานการณ์ของเศรฐกิจ</t>
+  </si>
+  <si>
+    <t>อีสาน</t>
+  </si>
+  <si>
+    <t>นากลาง 2</t>
+  </si>
+  <si>
+    <t>บจก.เคพีอาร์ คอนกรีต</t>
+  </si>
+  <si>
+    <t>ผู้ว่าลงนามอนุมัติผ่อนปรนพื้นที่เพื่อออก รง.4 แล้ว ส่งหนังสือให้ อบต.เพื่อติดประกาศทั้งจังหวัด</t>
+  </si>
+  <si>
+    <t>ไชยวาน</t>
+  </si>
+  <si>
+    <t>หจก.สมจินตนาคอนกรีต</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> รอพิจารณาการลงทุนใหม่ เนื่องจากเศรษฐกิจช่วงนี้ไม่ดี</t>
+  </si>
+  <si>
+    <t>เรณูนคร</t>
+  </si>
+  <si>
+    <t>หนองหาน-ทล.2350</t>
   </si>
 </sst>
 </file>
@@ -3468,7 +3802,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-101041E]d\ mmmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3535,6 +3869,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="SCG"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="SCG"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="10">
@@ -3691,7 +4038,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3977,6 +4324,54 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hyperlink_FC Type S -Update มิ.ย.54" xfId="2" xr:uid="{6FF725F9-9963-4974-9615-4E7862ED3C49}"/>
@@ -3986,7 +4381,377 @@
     <cellStyle name="Normal 3" xfId="5" xr:uid="{B66B5600-A50E-4622-AF93-9F956B928450}"/>
     <cellStyle name="Normal_FC Type S -Update มิ.ย.54 2" xfId="1" xr:uid="{BD1075EE-4223-4491-8ED9-9574F7136865}"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="85">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -12203,7 +12968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E2B2200-77E3-4247-A157-690BD36C0F87}">
-  <dimension ref="A1:Q298"/>
+  <dimension ref="A1:Q330"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
@@ -27305,6 +28070,1492 @@
         <v>1045</v>
       </c>
     </row>
+    <row r="299" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A299" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B299" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C299" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D299" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E299" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F299" s="33" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G299" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="H299" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="I299" s="29" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J299" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K299" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="L299" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="M299" s="31">
+        <v>2551</v>
+      </c>
+      <c r="N299" s="29"/>
+      <c r="O299" s="31"/>
+      <c r="P299" s="32"/>
+      <c r="Q299" s="28" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="300" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A300" s="46" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B300" s="18" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C300" s="18" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D300" s="18" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E300" s="18" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F300" s="18" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G300" s="18" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H300" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="I300" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J300" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K300" s="46" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L300" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="M300" s="48">
+        <v>2549</v>
+      </c>
+      <c r="N300" s="46"/>
+      <c r="O300" s="48"/>
+      <c r="P300" s="21"/>
+      <c r="Q300" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="301" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A301" s="10" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E301" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F301" s="15" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G301" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="H301" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I301" s="49" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J301" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="K301" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L301" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="M301" s="51">
+        <v>2548</v>
+      </c>
+      <c r="N301" s="49"/>
+      <c r="O301" s="51"/>
+      <c r="P301" s="13"/>
+      <c r="Q301" s="15" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="302" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A302" s="46" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B302" s="39" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C302" s="39" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D302" s="39" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E302" s="39" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F302" s="18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G302" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="H302" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="I302" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J302" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K302" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="L302" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="M302" s="48">
+        <v>2552</v>
+      </c>
+      <c r="N302" s="46"/>
+      <c r="O302" s="48"/>
+      <c r="P302" s="21"/>
+      <c r="Q302" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="303" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A303" s="46" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B303" s="39" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C303" s="39" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D303" s="39" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E303" s="39" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F303" s="18" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G303" s="39" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H303" s="18" t="s">
+        <v>1193</v>
+      </c>
+      <c r="I303" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J303" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K303" s="40" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L303" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="M303" s="48">
+        <v>2557</v>
+      </c>
+      <c r="N303" s="46"/>
+      <c r="O303" s="48"/>
+      <c r="P303" s="21"/>
+      <c r="Q303" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="304" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A304" s="10" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B304" s="80" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C304" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E304" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F304" s="15" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G304" s="15" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H304" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I304" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J304" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K304" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L304" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M304" s="12">
+        <v>2551</v>
+      </c>
+      <c r="N304" s="10"/>
+      <c r="O304" s="12"/>
+      <c r="P304" s="13"/>
+      <c r="Q304" s="9" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="305" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A305" s="43" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B305" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="C305" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="D305" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="E305" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="F305" s="33" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G305" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="H305" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="I305" s="43" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J305" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="K305" s="29" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L305" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="M305" s="45">
+        <v>2558</v>
+      </c>
+      <c r="N305" s="43"/>
+      <c r="O305" s="45"/>
+      <c r="P305" s="32"/>
+      <c r="Q305" s="33" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="306" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A306" s="49" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B306" s="80" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C306" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D306" s="15" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E306" s="15" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F306" s="15" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G306" s="15" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H306" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="I306" s="49" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J306" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="K306" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L306" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="M306" s="12">
+        <v>2549</v>
+      </c>
+      <c r="N306" s="49"/>
+      <c r="O306" s="51"/>
+      <c r="P306" s="13"/>
+      <c r="Q306" s="15" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="307" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A307" s="46" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B307" s="18" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C307" s="18" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D307" s="18" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E307" s="18" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F307" s="18" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G307" s="18" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H307" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="I307" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J307" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K307" s="46" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L307" s="47"/>
+      <c r="M307" s="42">
+        <v>2567</v>
+      </c>
+      <c r="N307" s="46"/>
+      <c r="O307" s="48"/>
+      <c r="P307" s="21"/>
+      <c r="Q307" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="308" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A308" s="29" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B308" s="85" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C308" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="D308" s="26" t="s">
+        <v>352</v>
+      </c>
+      <c r="E308" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="F308" s="33" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G308" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="H308" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="I308" s="29" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J308" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K308" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="L308" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M308" s="31">
+        <v>2558</v>
+      </c>
+      <c r="N308" s="29"/>
+      <c r="O308" s="31"/>
+      <c r="P308" s="32"/>
+      <c r="Q308" s="28" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="309" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A309" s="29" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B309" s="82" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C309" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="D309" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="E309" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="F309" s="33" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G309" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="H309" s="28" t="s">
+        <v>394</v>
+      </c>
+      <c r="I309" s="29" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J309" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K309" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="L309" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="M309" s="31">
+        <v>2550</v>
+      </c>
+      <c r="N309" s="29"/>
+      <c r="O309" s="31"/>
+      <c r="P309" s="32"/>
+      <c r="Q309" s="28" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="310" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A310" s="10" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B310" s="80" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="D310" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="E310" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F310" s="15" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G310" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="H310" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="I310" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J310" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K310" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L310" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="M310" s="12">
+        <v>2553</v>
+      </c>
+      <c r="N310" s="10"/>
+      <c r="O310" s="12"/>
+      <c r="P310" s="13"/>
+      <c r="Q310" s="9" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="311" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A311" s="29" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B311" s="82" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C311" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="D311" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="E311" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="F311" s="33" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G311" s="33" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H311" s="33" t="s">
+        <v>418</v>
+      </c>
+      <c r="I311" s="43" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J311" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="K311" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="L311" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="M311" s="31">
+        <v>2549</v>
+      </c>
+      <c r="N311" s="43"/>
+      <c r="O311" s="45"/>
+      <c r="P311" s="32"/>
+      <c r="Q311" s="33" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="312" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A312" s="10" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B312" s="80" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D312" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E312" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="F312" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G312" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="H312" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="I312" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J312" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K312" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L312" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M312" s="12">
+        <v>2551</v>
+      </c>
+      <c r="N312" s="10"/>
+      <c r="O312" s="12"/>
+      <c r="P312" s="13"/>
+      <c r="Q312" s="9" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="313" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A313" s="46" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B313" s="81" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C313" s="18" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D313" s="18" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E313" s="18" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F313" s="18" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G313" s="18" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H313" s="18" t="s">
+        <v>1194</v>
+      </c>
+      <c r="I313" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J313" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K313" s="46" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L313" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="M313" s="42">
+        <v>2551</v>
+      </c>
+      <c r="N313" s="46"/>
+      <c r="O313" s="48"/>
+      <c r="P313" s="21"/>
+      <c r="Q313" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="314" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A314" s="46" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B314" s="81" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C314" s="18" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D314" s="18" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E314" s="18" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F314" s="18" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G314" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="H314" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="I314" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J314" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K314" s="46" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L314" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="M314" s="42">
+        <v>2557</v>
+      </c>
+      <c r="N314" s="46"/>
+      <c r="O314" s="48"/>
+      <c r="P314" s="21"/>
+      <c r="Q314" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="315" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A315" s="46" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B315" s="81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C315" s="18" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D315" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E315" s="18" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F315" s="18" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G315" s="18" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H315" s="18" t="s">
+        <v>594</v>
+      </c>
+      <c r="I315" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J315" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K315" s="46" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L315" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="M315" s="42">
+        <v>2558</v>
+      </c>
+      <c r="N315" s="46"/>
+      <c r="O315" s="48"/>
+      <c r="P315" s="21"/>
+      <c r="Q315" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="316" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A316" s="10" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B316" s="80" t="s">
+        <v>603</v>
+      </c>
+      <c r="C316" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="D316" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="E316" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="F316" s="15" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G316" s="15" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H316" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="I316" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J316" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K316" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L316" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M316" s="12">
+        <v>2553</v>
+      </c>
+      <c r="N316" s="10"/>
+      <c r="O316" s="12"/>
+      <c r="P316" s="13"/>
+      <c r="Q316" s="9" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="317" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A317" s="49" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B317" s="86" t="s">
+        <v>633</v>
+      </c>
+      <c r="C317" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="D317" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="E317" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="F317" s="15" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G317" s="15" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H317" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="I317" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J317" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K317" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L317" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="M317" s="12">
+        <v>2561</v>
+      </c>
+      <c r="N317" s="10"/>
+      <c r="O317" s="12"/>
+      <c r="P317" s="13"/>
+      <c r="Q317" s="9" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="318" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A318" s="29" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B318" s="82" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C318" s="26" t="s">
+        <v>548</v>
+      </c>
+      <c r="D318" s="33" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E318" s="33" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F318" s="33" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G318" s="33" t="s">
+        <v>640</v>
+      </c>
+      <c r="H318" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="I318" s="43" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J318" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="K318" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="L318" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="M318" s="45">
+        <v>2559</v>
+      </c>
+      <c r="N318" s="43"/>
+      <c r="O318" s="45"/>
+      <c r="P318" s="32"/>
+      <c r="Q318" s="33" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="319" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A319" s="46" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B319" s="81" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C319" s="18" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D319" s="18" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E319" s="18" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F319" s="18" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G319" s="18" t="s">
+        <v>582</v>
+      </c>
+      <c r="H319" s="18" t="s">
+        <v>582</v>
+      </c>
+      <c r="I319" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J319" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K319" s="46" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L319" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="M319" s="48">
+        <v>2554</v>
+      </c>
+      <c r="N319" s="46"/>
+      <c r="O319" s="48"/>
+      <c r="P319" s="21"/>
+      <c r="Q319" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="320" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A320" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B320" s="80" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C320" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="D320" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="F320" s="15" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G320" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="H320" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="I320" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J320" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K320" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L320" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M320" s="12">
+        <v>2556</v>
+      </c>
+      <c r="N320" s="10"/>
+      <c r="O320" s="12"/>
+      <c r="P320" s="13"/>
+      <c r="Q320" s="9" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="321" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A321" s="29" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B321" s="82" t="s">
+        <v>719</v>
+      </c>
+      <c r="C321" s="26" t="s">
+        <v>719</v>
+      </c>
+      <c r="D321" s="27" t="s">
+        <v>720</v>
+      </c>
+      <c r="E321" s="26" t="s">
+        <v>719</v>
+      </c>
+      <c r="F321" s="33" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G321" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="H321" s="28" t="s">
+        <v>678</v>
+      </c>
+      <c r="I321" s="29" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J321" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K321" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="L321" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="M321" s="31">
+        <v>2556</v>
+      </c>
+      <c r="N321" s="29"/>
+      <c r="O321" s="31"/>
+      <c r="P321" s="32"/>
+      <c r="Q321" s="28" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="322" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A322" s="29" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B322" s="82" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C322" s="26" t="s">
+        <v>771</v>
+      </c>
+      <c r="D322" s="27" t="s">
+        <v>772</v>
+      </c>
+      <c r="E322" s="26" t="s">
+        <v>771</v>
+      </c>
+      <c r="F322" s="33" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G322" s="26" t="s">
+        <v>774</v>
+      </c>
+      <c r="H322" s="28" t="s">
+        <v>774</v>
+      </c>
+      <c r="I322" s="29" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J322" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K322" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="L322" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="M322" s="31">
+        <v>2556</v>
+      </c>
+      <c r="N322" s="29"/>
+      <c r="O322" s="31"/>
+      <c r="P322" s="32"/>
+      <c r="Q322" s="28" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="323" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A323" s="46" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B323" s="18" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C323" s="18" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D323" s="18" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E323" s="18" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F323" s="18" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G323" s="18" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H323" s="18" t="s">
+        <v>726</v>
+      </c>
+      <c r="I323" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J323" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K323" s="46" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L323" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="M323" s="48">
+        <v>2554</v>
+      </c>
+      <c r="N323" s="46"/>
+      <c r="O323" s="48"/>
+      <c r="P323" s="21"/>
+      <c r="Q323" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="324" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A324" s="46" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B324" s="18" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C324" s="18" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D324" s="18" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E324" s="18" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F324" s="18" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G324" s="18" t="s">
+        <v>660</v>
+      </c>
+      <c r="H324" s="18" t="s">
+        <v>660</v>
+      </c>
+      <c r="I324" s="46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J324" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K324" s="46" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L324" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="M324" s="48">
+        <v>2550</v>
+      </c>
+      <c r="N324" s="46"/>
+      <c r="O324" s="48"/>
+      <c r="P324" s="21"/>
+      <c r="Q324" s="18" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="325" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A325" s="49" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C325" s="9" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D325" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E325" s="9" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F325" s="15" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G325" s="15" t="s">
+        <v>906</v>
+      </c>
+      <c r="H325" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="I325" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J325" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K325" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L325" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="M325" s="12">
+        <v>2551</v>
+      </c>
+      <c r="N325" s="10"/>
+      <c r="O325" s="12"/>
+      <c r="P325" s="13"/>
+      <c r="Q325" s="9" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="326" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A326" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B326" s="80" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C326" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="D326" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="E326" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="F326" s="15" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G326" s="15" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H326" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="I326" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J326" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K326" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L326" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="M326" s="12">
+        <v>2553</v>
+      </c>
+      <c r="N326" s="10"/>
+      <c r="O326" s="12"/>
+      <c r="P326" s="13"/>
+      <c r="Q326" s="9" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="327" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A327" s="49" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C327" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D327" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E327" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F327" s="15" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G327" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H327" s="15" t="s">
+        <v>811</v>
+      </c>
+      <c r="I327" s="49" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J327" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="K327" s="49" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L327" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="M327" s="51">
+        <v>2550</v>
+      </c>
+      <c r="N327" s="49"/>
+      <c r="O327" s="51"/>
+      <c r="P327" s="13"/>
+      <c r="Q327" s="15" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="328" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A328" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B328" s="15" t="s">
+        <v>984</v>
+      </c>
+      <c r="C328" s="15" t="s">
+        <v>984</v>
+      </c>
+      <c r="D328" s="15" t="s">
+        <v>985</v>
+      </c>
+      <c r="E328" s="15" t="s">
+        <v>984</v>
+      </c>
+      <c r="F328" s="15" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G328" s="15" t="s">
+        <v>754</v>
+      </c>
+      <c r="H328" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="I328" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J328" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K328" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L328" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="M328" s="12">
+        <v>2558</v>
+      </c>
+      <c r="N328" s="10"/>
+      <c r="O328" s="12"/>
+      <c r="P328" s="13"/>
+      <c r="Q328" s="9" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="329" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A329" s="40" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B329" s="22" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C329" s="22" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D329" s="22" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E329" s="22" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F329" s="23"/>
+      <c r="G329" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H329" s="24"/>
+      <c r="I329" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J329" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K329" s="24"/>
+      <c r="L329" s="24"/>
+      <c r="M329" s="24">
+        <v>2568</v>
+      </c>
+      <c r="N329" s="24"/>
+      <c r="O329" s="24"/>
+      <c r="P329" s="113"/>
+      <c r="Q329" s="23" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="330" spans="1:17" ht="17.5" thickBot="1">
+      <c r="A330" s="24" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B330" s="23" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C330" s="23" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D330" s="22" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E330" s="23" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F330" s="23"/>
+      <c r="G330" s="23" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H330" s="24"/>
+      <c r="I330" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J330" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K330" s="24"/>
+      <c r="L330" s="24"/>
+      <c r="M330" s="24">
+        <v>2569</v>
+      </c>
+      <c r="N330" s="24"/>
+      <c r="O330" s="24"/>
+      <c r="P330" s="113"/>
+      <c r="Q330" s="23" t="s">
+        <v>1195</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:Q298" xr:uid="{EEF4DB50-2D81-44EF-A62B-379133D03144}">
     <sortState ref="A3:Q298">
@@ -27321,171 +29572,220 @@
     <mergeCell ref="N1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="M2 O2">
-    <cfRule type="cellIs" dxfId="44" priority="56" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="69" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2">
-    <cfRule type="cellIs" dxfId="43" priority="53" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="66" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K139 J297:K65341 K296 J93:K119 J141:K214 J121:K138 J1:K91 J216:K270 J272:K294">
-    <cfRule type="cellIs" dxfId="42" priority="43" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="K139 J297:K298 K296 J93:K119 J141:K214 J121:K138 J1:K91 J216:K270 J272:K294 J331:K65341 K329:K330">
+    <cfRule type="cellIs" dxfId="82" priority="56" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="44" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="57" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="45" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="58" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J270:K270 J272:K274">
-    <cfRule type="cellIs" dxfId="39" priority="40" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="53" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="41" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="54" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="42" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="55" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J140:K140">
-    <cfRule type="cellIs" dxfId="36" priority="37" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="50" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="38" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="51" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="39" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="52" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J139">
-    <cfRule type="cellIs" dxfId="33" priority="34" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="47" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="35" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="48" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="36" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="49" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J92">
-    <cfRule type="cellIs" dxfId="30" priority="29" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="42" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="30" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="43" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="31" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="44" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K120">
-    <cfRule type="cellIs" dxfId="27" priority="26" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="39" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="27" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="40" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="28" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="41" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J120">
-    <cfRule type="cellIs" dxfId="24" priority="23" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="36" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="24" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="37" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="25" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="38" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J295">
-    <cfRule type="cellIs" dxfId="21" priority="20" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="33" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="21" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="34" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="22" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="35" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K295">
-    <cfRule type="cellIs" dxfId="18" priority="17" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="30" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="18" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="31" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="19" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="32" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J296">
-    <cfRule type="cellIs" dxfId="15" priority="14" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="27" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="15" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="28" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="16" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="29" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K92">
-    <cfRule type="cellIs" dxfId="12" priority="11" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="24" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="12" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="25" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="13" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="26" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N69:O69">
-    <cfRule type="cellIs" dxfId="9" priority="10" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="23" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J215:K215">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="20" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="21" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="22" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J271:K271">
-    <cfRule type="cellIs" dxfId="5" priority="4" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="17" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="18" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="19" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J271:K271">
-    <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="14" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="15" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="16" stopIfTrue="1" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J299:K328">
+    <cfRule type="cellIs" dxfId="18" priority="11" stopIfTrue="1" operator="equal">
+      <formula>"ปิดชั่วคราว"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="12" stopIfTrue="1" operator="equal">
+      <formula>"CLOSE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="13" stopIfTrue="1" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M299">
+    <cfRule type="cellIs" dxfId="15" priority="10" stopIfTrue="1" operator="equal">
+      <formula>"CLOSE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J328:K328">
+    <cfRule type="cellIs" dxfId="14" priority="7" stopIfTrue="1" operator="equal">
+      <formula>"ปิดชั่วคราว"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="8" stopIfTrue="1" operator="equal">
+      <formula>"CLOSE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="9" stopIfTrue="1" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J329:J330">
+    <cfRule type="cellIs" dxfId="11" priority="4" stopIfTrue="1" operator="equal">
+      <formula>"ปิดชั่วคราว"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="5" stopIfTrue="1" operator="equal">
+      <formula>"CLOSE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="6" stopIfTrue="1" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J329:J330">
+    <cfRule type="cellIs" dxfId="8" priority="1" stopIfTrue="1" operator="equal">
+      <formula>"ปิดชั่วคราว"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="equal">
+      <formula>"CLOSE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="3" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27496,4 +29796,379 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFDD7D9-162C-471A-9FE0-F8A47E6B16B1}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="15.5"/>
+  <cols>
+    <col min="1" max="1" width="10" style="130" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="116" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" style="116" customWidth="1"/>
+    <col min="4" max="4" width="5.90625" style="131" customWidth="1"/>
+    <col min="5" max="5" width="30.54296875" style="130" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" style="132" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" style="116" customWidth="1"/>
+    <col min="8" max="8" width="77.7265625" style="116" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="116"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="116" customFormat="1" ht="31.5" thickBot="1">
+      <c r="A1" s="114" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="114" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="114" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="114" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E1" s="114" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F1" s="115" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G1" s="114" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H1" s="114" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A2" s="117" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B2" s="118" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C2" s="119" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="117" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="122" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H2" s="122" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A3" s="123" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B3" s="124" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C3" s="122" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="117" t="s">
+        <v>414</v>
+      </c>
+      <c r="F3" s="125" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="122"/>
+    </row>
+    <row r="4" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A4" s="123" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B4" s="124" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C4" s="122" t="s">
+        <v>418</v>
+      </c>
+      <c r="D4" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="117" t="s">
+        <v>414</v>
+      </c>
+      <c r="F4" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="122" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H4" s="122" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A5" s="126" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B5" s="127" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C5" s="127" t="s">
+        <v>549</v>
+      </c>
+      <c r="D5" s="128" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E5" s="126" t="s">
+        <v>653</v>
+      </c>
+      <c r="F5" s="129" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="122"/>
+    </row>
+    <row r="6" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A6" s="126" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B6" s="127" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C6" s="127" t="s">
+        <v>582</v>
+      </c>
+      <c r="D6" s="128" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E6" s="126" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F6" s="128" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="124" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H6" s="122" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A7" s="126" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B7" s="127" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C7" s="127" t="s">
+        <v>485</v>
+      </c>
+      <c r="D7" s="128" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="126" t="s">
+        <v>548</v>
+      </c>
+      <c r="F7" s="128" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="122" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H7" s="122" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A8" s="123" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B8" s="124" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C8" s="122" t="s">
+        <v>832</v>
+      </c>
+      <c r="D8" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="117" t="s">
+        <v>841</v>
+      </c>
+      <c r="F8" s="125" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="122"/>
+    </row>
+    <row r="9" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A9" s="123" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C9" s="122" t="s">
+        <v>789</v>
+      </c>
+      <c r="D9" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="117" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F9" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="122" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H9" s="122" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A10" s="123" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B10" s="124" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C10" s="122" t="s">
+        <v>663</v>
+      </c>
+      <c r="D10" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="117" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F10" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="122" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H10" s="122" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A11" s="123" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B11" s="124" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C11" s="122" t="s">
+        <v>687</v>
+      </c>
+      <c r="D11" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="117"/>
+      <c r="F11" s="114" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="122" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H11" s="122"/>
+    </row>
+    <row r="12" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A12" s="123" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B12" s="124" t="s">
+        <v>873</v>
+      </c>
+      <c r="C12" s="122" t="s">
+        <v>873</v>
+      </c>
+      <c r="D12" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="117" t="s">
+        <v>870</v>
+      </c>
+      <c r="F12" s="120" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="122"/>
+    </row>
+    <row r="13" spans="1:8" s="116" customFormat="1" ht="16" thickBot="1">
+      <c r="A13" s="123" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B13" s="124" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C13" s="122" t="s">
+        <v>663</v>
+      </c>
+      <c r="D13" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="117" t="s">
+        <v>760</v>
+      </c>
+      <c r="F13" s="129" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="122"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F8 F1:F6 F11:F12 F14:F1048576">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:F10">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/OPENFC.xlsx
+++ b/OPENFC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7627B2C0-9649-41C1-8440-CD34F9CB95F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4089CEFC-9AC7-4889-A66E-786EEF7B2DF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3C536319-8C24-4021-B9D4-FBD21F6BCA84}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" activeTab="1" xr2:uid="{3C536319-8C24-4021-B9D4-FBD21F6BCA84}"/>
   </bookViews>
   <sheets>
     <sheet name="OPEN FC" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4389" uniqueCount="1235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4388" uniqueCount="1233">
   <si>
     <t>เปิดโรงงาน</t>
   </si>
@@ -3750,15 +3750,6 @@
     <t>NX</t>
   </si>
   <si>
-    <t>บูรพา ท่าใหม่</t>
-  </si>
-  <si>
-    <t>บจก.บูรพาคอนกรีตแอนคอนสตั๊กชั่น</t>
-  </si>
-  <si>
-    <t xml:space="preserve">รอการปรับปรุงระบบsafety และสิ่งแวดล้อม F27,F28  </t>
-  </si>
-  <si>
     <t>บ้านสร้าง</t>
   </si>
   <si>
@@ -3802,6 +3793,9 @@
   </si>
   <si>
     <t>วี.เอส.คอนกรีต 3 ลาดตะเคียน (Type X)</t>
+  </si>
+  <si>
+    <t>VS คอนกรีต 4</t>
   </si>
 </sst>
 </file>
@@ -4407,14 +4401,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4474,7 +4461,14 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -13966,7 +13960,7 @@
         <v>16</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="17.5" thickBot="1">
@@ -15963,10 +15957,10 @@
         <v>653</v>
       </c>
       <c r="F45" s="66" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="G45" s="64" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="H45" s="18" t="s">
         <v>549</v>
@@ -29681,13 +29675,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J45:K45">
-    <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" stopIfTrue="1" operator="equal">
       <formula>"ปิดชั่วคราว"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="equal">
       <formula>"CLOSE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" stopIfTrue="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29847,16 +29841,16 @@
         <v>1214</v>
       </c>
       <c r="B6" s="124" t="s">
-        <v>1217</v>
+        <v>1232</v>
       </c>
       <c r="C6" s="124" t="s">
-        <v>582</v>
+        <v>549</v>
       </c>
       <c r="D6" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="E6" s="123" t="s">
-        <v>1218</v>
+        <v>653</v>
       </c>
       <c r="F6" s="125" t="s">
         <v>25</v>
@@ -29864,16 +29858,14 @@
       <c r="G6" s="121" t="s">
         <v>1209</v>
       </c>
-      <c r="H6" s="119" t="s">
-        <v>1219</v>
-      </c>
+      <c r="H6" s="119"/>
     </row>
     <row r="7" spans="1:8" ht="16" thickBot="1">
       <c r="A7" s="123" t="s">
         <v>1214</v>
       </c>
       <c r="B7" s="124" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="C7" s="124" t="s">
         <v>485</v>
@@ -29888,15 +29880,15 @@
         <v>109</v>
       </c>
       <c r="G7" s="119" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="H7" s="119" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16" thickBot="1">
       <c r="A8" s="120" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B8" s="121" t="s">
         <v>1043</v>
@@ -29920,10 +29912,10 @@
     </row>
     <row r="9" spans="1:8" ht="16" thickBot="1">
       <c r="A9" s="120" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B9" s="121" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="C9" s="119" t="s">
         <v>789</v>
@@ -29932,7 +29924,7 @@
         <v>23</v>
       </c>
       <c r="E9" s="114" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F9" s="122" t="s">
         <v>44</v>
@@ -29941,15 +29933,15 @@
         <v>1209</v>
       </c>
       <c r="H9" s="119" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16" thickBot="1">
       <c r="A10" s="120" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B10" s="121" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="C10" s="119" t="s">
         <v>663</v>
@@ -29958,24 +29950,24 @@
         <v>23</v>
       </c>
       <c r="E10" s="114" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="F10" s="122" t="s">
         <v>44</v>
       </c>
       <c r="G10" s="119" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="H10" s="119" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16" thickBot="1">
       <c r="A11" s="120" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B11" s="121" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="C11" s="119" t="s">
         <v>687</v>
@@ -29994,7 +29986,7 @@
     </row>
     <row r="12" spans="1:8" ht="16" thickBot="1">
       <c r="A12" s="120" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B12" s="121" t="s">
         <v>873</v>
@@ -30018,10 +30010,10 @@
     </row>
     <row r="13" spans="1:8" ht="16" thickBot="1">
       <c r="A13" s="120" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B13" s="121" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="C13" s="119" t="s">
         <v>663</v>
@@ -30042,32 +30034,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F8 F1:F6 F11:F12 F14:F1048576">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F10">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
